--- a/workshop_registration_form_templates/029_reptile_exhibition_registration--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/029_reptile_exhibition_registration--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'i_agree',_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'i_agree', 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'i_dont_agree',_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'i_dont_agree', 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'reptile_show',_'value':_'reptile_show'}</t>
+          <t>reptile_show</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'reptile_show', 'value': 'Reptile Show'}</t>
+          <t>Reptile Show</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'educational_event',_'value':_'educational_event'}</t>
+          <t>educational_event</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'educational_event', 'value': 'Educational Event'}</t>
+          <t>Educational Event</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'trade_show',_'value':_'trade_show'}</t>
+          <t>trade_show</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'trade_show', 'value': 'Trade Show'}</t>
+          <t>Trade Show</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'reptile',_'value':_'reptile'}</t>
+          <t>reptile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'reptile', 'value': 'Reptile'}</t>
+          <t>Reptile</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'on_site',_'value':_'on_site'}</t>
+          <t>on_site</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'on_site', 'value': 'On Site'}</t>
+          <t>On Site</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'off_site',_'value':_'off_site'}</t>
+          <t>off_site</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'off_site', 'value': 'Off Site'}</t>
+          <t>Off Site</t>
         </is>
       </c>
     </row>
